--- a/client-report/client-directory-report.xlsx
+++ b/client-report/client-directory-report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="378">
   <si>
     <t>Отчёт по размещению компании в каталогах</t>
   </si>
@@ -56,37 +56,55 @@
     <t>Размещено (подтверждено)</t>
   </si>
   <si>
-    <t>Профиль компании успешно создан и доступен (Semfirms, FindUsHere)</t>
+    <t>Найден публичный профиль URL и размещение подтверждено (Semfirms, FindUsHere)</t>
   </si>
   <si>
     <t>Заявка отправлена</t>
   </si>
   <si>
-    <t>Форма размещения заполнена и отправлена, ожидается обработка площадкой (в т.ч. Brownbook, CityLocalPro 07.08)</t>
+    <t>Форма отправлена, публикация/профиль ещё не подтверждены (Brownbook, CityLocalPro, DesignRush, GoodFirms, Digital Agency Net, Plantation Chamber)</t>
   </si>
   <si>
     <t>Аккаунт создан</t>
   </si>
   <si>
-    <t>Создан аккаунт, требуется дальнейшее заполнение или публикация профиля</t>
-  </si>
-  <si>
-    <t>Требуется действие</t>
-  </si>
-  <si>
-    <t>Нужен ручной шаг: подтверждение, CAPTCHA, заполнение профиля или другие действия</t>
+    <t>Аккаунт создан, требуется заполнение профиля, публикация контента или завершение регистрации (Crunchbase, Medium, Shopify Partners, YouTube Channel)</t>
+  </si>
+  <si>
+    <t>Ожидает модерации</t>
+  </si>
+  <si>
+    <t>Площадка получила заявку и выполняет проверку</t>
+  </si>
+  <si>
+    <t>Требуется подтверждение</t>
+  </si>
+  <si>
+    <t>Требуется подтверждение email/телефона для активации размещения</t>
+  </si>
+  <si>
+    <t>Требуется ручное действие</t>
+  </si>
+  <si>
+    <t>Ручной шаг: CAPTCHA, OAuth, зависший submit, партнёрская/плановая заявка или решение пользователя</t>
+  </si>
+  <si>
+    <t>Заблокировано защитой сайта</t>
+  </si>
+  <si>
+    <t>Внешняя блокировка: Cloudflare, CAPTCHA challenge, IP restriction — только ручной заход</t>
   </si>
   <si>
     <t>Не удалось выполнить</t>
   </si>
   <si>
-    <t>Площадка недоступна, заблокирована (в т.ч. Cloudflare/anti-bot) или возникла техническая проблема</t>
+    <t>Сайт недоступен, регистрация отсутствует (404) или техническая ошибка</t>
   </si>
   <si>
     <t>Не подходит для размещения</t>
   </si>
   <si>
-    <t>Ресурс не является стандартным каталогом компаний или требует другого подхода</t>
+    <t>Ресурс не является стандартным каталогом компаний, требует другого подхода или платного членства</t>
   </si>
   <si>
     <t>Важная информация</t>
@@ -101,9 +119,10 @@
   </si>
   <si>
     <t xml:space="preserve">Приоритет дальнейшей работы:
-1. Завершение площадок, где уже создан аккаунт или отправлена заявка.
-2. Обработка площадок, требующих ручного действия.
-3. Дополнение профилей и получение прямых ссылок на размещения.</t>
+1. Отслеживание SUBMITTED/PENDING: подтвердить email (Brownbook), дождаться модерации (CityLocalPro), проверить публичные профили.
+2. Завершение REGISTERED: заполнить профили Crunchbase, Medium, Shopify Partners, YouTube Channel.
+3. Обработка NEEDS_MANUAL: TopSEOs (LinkedIn OAuth).
+4. Повторные регистрации для SUBMITTED/REGISTERED/PENDING/BLOCKED НЕ запускать.</t>
   </si>
   <si>
     <t>Каталог</t>
@@ -151,61 +170,64 @@
     <t>Заблокировано Cloudflare/anti-bot — требуется ручной заход</t>
   </si>
   <si>
+    <t>Ручной заход через обычный браузер / другой IP</t>
+  </si>
+  <si>
+    <t>Внешняя блокировка: Cloudflare / CAPTCHA / IP restriction</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Manta</t>
+  </si>
+  <si>
+    <t>https://www.manta.com</t>
+  </si>
+  <si>
+    <t>Hotfrog</t>
+  </si>
+  <si>
+    <t>https://www.hotfrog.com</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>Alignable</t>
+  </si>
+  <si>
+    <t>https://www.alignable.com</t>
+  </si>
+  <si>
+    <t>Требуется ручное действие (повторить заполнение или завершить отправку)</t>
+  </si>
+  <si>
+    <t>CAPTCHA, OAuth, зависший submit, партнёрская/плановая заявка или решение пользователя</t>
+  </si>
+  <si>
+    <t>Superpages</t>
+  </si>
+  <si>
+    <t>https://www.superpages.com</t>
+  </si>
+  <si>
+    <t>Заблокировано Cloudflare challenge — требуется ручной заход</t>
+  </si>
+  <si>
+    <t>Merchant Circle</t>
+  </si>
+  <si>
+    <t>https://www.merchantcircle.com</t>
+  </si>
+  <si>
+    <t>Регистрация недоступна (404/403) — требуется ручная проверка</t>
+  </si>
+  <si>
     <t>Проверить альтернативный способ размещения</t>
   </si>
   <si>
-    <t>Сайт недоступен / ограничение доступа / техническая ошибка</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Manta</t>
-  </si>
-  <si>
-    <t>https://www.manta.com</t>
-  </si>
-  <si>
-    <t>Hotfrog</t>
-  </si>
-  <si>
-    <t>https://www.hotfrog.com</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>Alignable</t>
-  </si>
-  <si>
-    <t>https://www.alignable.com</t>
-  </si>
-  <si>
-    <t>Требуется ручное действие</t>
-  </si>
-  <si>
-    <t>Требуется ручное действие (повторить заполнение или завершить отправку)</t>
-  </si>
-  <si>
-    <t>Требуется CAPTCHA, подтверждение, ручной шаг или дополнительная регистрация</t>
-  </si>
-  <si>
-    <t>Superpages</t>
-  </si>
-  <si>
-    <t>https://www.superpages.com</t>
-  </si>
-  <si>
-    <t>Доступ ограничен защитой сайта</t>
-  </si>
-  <si>
-    <t>Merchant Circle</t>
-  </si>
-  <si>
-    <t>https://www.merchantcircle.com</t>
-  </si>
-  <si>
-    <t>Регистрация недоступна (404/403) — требуется ручная проверка</t>
+    <t>Сайт недоступен / техническая ошибка</t>
   </si>
   <si>
     <t>Local.com</t>
@@ -232,10 +254,10 @@
     <t>Заявка отправлена 07.08, профиль не опубликован (поиск: Results Found 0) — ожидает email-подтверждения/модерации</t>
   </si>
   <si>
-    <t>Ожидать обработки площадкой</t>
-  </si>
-  <si>
-    <t>Форма размещения заполнена и отправлена</t>
+    <t>Ожидать обработки площадкой и проверить публичный профиль</t>
+  </si>
+  <si>
+    <t>Форма размещения заполнена и отправлена, профиль ещё не подтверждён</t>
   </si>
   <si>
     <t>не подтверждён (профиль не найден)</t>
@@ -247,7 +269,7 @@
     <t>https://www.opendi.us</t>
   </si>
   <si>
-    <t>Сайт блокирует доступ (защита сайта); требуется другой IP/VPN или ручной заход</t>
+    <t>Заблокировано Cloudflare/IP-reputation — требуется другой IP/VPN или ручной заход</t>
   </si>
   <si>
     <t>Spoke</t>
@@ -274,7 +296,7 @@
     <t>https://www.n49.com</t>
   </si>
   <si>
-    <t>Доступ ограничен (403), нет формы размещения</t>
+    <t>Доступ ограничен (403/IP restriction) — требуется ручной заход</t>
   </si>
   <si>
     <t>FindUsHere</t>
@@ -289,7 +311,7 @@
     <t>Проверка завершена</t>
   </si>
   <si>
-    <t>Профиль компании создан и доступен</t>
+    <t>Найден публичный профиль URL</t>
   </si>
   <si>
     <t>https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/</t>
@@ -331,6 +353,9 @@
     <t>https://themanifest.com</t>
   </si>
   <si>
+    <t>Заблокировано Cloudflare challenge-loop на vendor.clutch.co/profile/create/basic (реальная форма регистрации). Главная clutch.co/get-listed грузится, но vendor-портал не отвечает после CF verification (Ray ID a27c85757b9b543b) — требуется ручной заход в обычном браузере</t>
+  </si>
+  <si>
     <t>Upcity</t>
   </si>
   <si>
@@ -355,9 +380,6 @@
     <t>https://www.sortlist.com</t>
   </si>
   <si>
-    <t>Доступ ограничен защитой сайта — требуется ручной заход</t>
-  </si>
-  <si>
     <t>Bark.com</t>
   </si>
   <si>
@@ -391,7 +413,7 @@
     <t>https://www.topseos.com</t>
   </si>
   <si>
-    <t>Форма заполняется, отправка зависает — нужен ручной шаг</t>
+    <t>Регистрация только через LinkedIn OAuth — нужен ручной вход</t>
   </si>
   <si>
     <t>Influencer Mkt Hub</t>
@@ -448,7 +470,7 @@
     <t>https://www.ftlchamber.com</t>
   </si>
   <si>
-    <t>Заявка на членство требует регистрации и ручного шага</t>
+    <t>Платное членство ($574/год + $50 one-time, non-refundable) — требуется отдельное одобрение клиента и бюджет</t>
   </si>
   <si>
     <t>Miami Chamber</t>
@@ -466,9 +488,6 @@
     <t>https://business.nextdoor.com</t>
   </si>
   <si>
-    <t>Подтверждение по почтовой открытке</t>
-  </si>
-  <si>
     <t>CityLocalPro</t>
   </si>
   <si>
@@ -517,7 +536,7 @@
     <t>E</t>
   </si>
   <si>
-    <t>Форма найдена, требуется ручное заполнение</t>
+    <t>Ресурс не является каталогом бизнеса (government mentoring) — не подходит для размещения</t>
   </si>
   <si>
     <t>FL DEO Business</t>
@@ -547,45 +566,45 @@
     <t>Partner Program</t>
   </si>
   <si>
+    <t>HubSpot Agency Dir</t>
+  </si>
+  <si>
+    <t>https://www.hubspot.com/agencies</t>
+  </si>
+  <si>
+    <t>Shopify Partners</t>
+  </si>
+  <si>
+    <t>https://www.shopify.com/partners</t>
+  </si>
+  <si>
+    <t>Партнёрский аккаунт создан</t>
+  </si>
+  <si>
+    <t>Заполнить профиль компании / завершить публикацию</t>
+  </si>
+  <si>
+    <t>Создан аккаунт, профиль ещё не опубликован</t>
+  </si>
+  <si>
+    <t>WooCommerce Agency</t>
+  </si>
+  <si>
+    <t>https://woocommerce.com/agencies</t>
+  </si>
+  <si>
+    <t>Форма подачи не найдена</t>
+  </si>
+  <si>
+    <t>Webflow Partner</t>
+  </si>
+  <si>
+    <t>https://webflow.com/partners</t>
+  </si>
+  <si>
     <t>Партнёрская программа (ручное ревью)</t>
   </si>
   <si>
-    <t>HubSpot Agency Dir</t>
-  </si>
-  <si>
-    <t>https://www.hubspot.com/agencies</t>
-  </si>
-  <si>
-    <t>Shopify Partners</t>
-  </si>
-  <si>
-    <t>https://www.shopify.com/partners</t>
-  </si>
-  <si>
-    <t>Партнёрский аккаунт создан</t>
-  </si>
-  <si>
-    <t>Заполнить профиль компании / завершить публикацию</t>
-  </si>
-  <si>
-    <t>Создан аккаунт, профиль ещё не опубликован</t>
-  </si>
-  <si>
-    <t>WooCommerce Agency</t>
-  </si>
-  <si>
-    <t>https://woocommerce.com/agencies</t>
-  </si>
-  <si>
-    <t>Форма подачи не найдена</t>
-  </si>
-  <si>
-    <t>Webflow Partner</t>
-  </si>
-  <si>
-    <t>https://webflow.com/partners</t>
-  </si>
-  <si>
     <t>Mailchimp Partner</t>
   </si>
   <si>
@@ -601,7 +620,7 @@
     <t>https://www.activecampaign.com/partners</t>
   </si>
   <si>
-    <t>Сайт доступен; форма заполнена частично, нет кнопки отправки</t>
+    <t>Партнёрская программа (reseller/commission), не каталог — публичногоListing нет</t>
   </si>
   <si>
     <t>Stripe Partner</t>
@@ -673,9 +692,6 @@
     <t>https://wellfound.com</t>
   </si>
   <si>
-    <t>Требуется аккаунт и профиль (SPA)</t>
-  </si>
-  <si>
     <t>ProductHunt</t>
   </si>
   <si>
@@ -805,25 +821,13 @@
     <t>B</t>
   </si>
   <si>
-    <t>Claim через верификацию домена (нужна почта домена)</t>
-  </si>
-  <si>
-    <t>Sitejabber</t>
-  </si>
-  <si>
-    <t>https://www.sitejabber.com</t>
-  </si>
-  <si>
-    <t>Аккаунт создавался ранее; требуется ручная проверка</t>
-  </si>
-  <si>
     <t>ProvenExpert</t>
   </si>
   <si>
     <t>https://www.provenexpert.com</t>
   </si>
   <si>
-    <t>Сайт блокирует соединение (ERR_CONNECTION_CLOSED) — требуется ручная проверка</t>
+    <t>Сайт блокирует соединение (ERR_CONNECTION_CLOSED) — внешняя блокировка</t>
   </si>
   <si>
     <t>G2</t>
@@ -832,9 +836,6 @@
     <t>https://www.g2.com</t>
   </si>
   <si>
-    <t>Форма подачи ограничена защитой сайта; требуется ручное действие</t>
-  </si>
-  <si>
     <t>Data Axle</t>
   </si>
   <si>
@@ -859,18 +860,12 @@
     <t>https://www.expressupdate.com</t>
   </si>
   <si>
-    <t>Claim через телефон/почту</t>
-  </si>
-  <si>
     <t>Foursquare Business</t>
   </si>
   <si>
     <t>https://business.foursquare.com</t>
   </si>
   <si>
-    <t>Верификация по телефону</t>
-  </si>
-  <si>
     <t>Причина</t>
   </si>
   <si>
@@ -883,12 +878,18 @@
     <t>Требуется другой подход</t>
   </si>
   <si>
+    <t>Для размещения требуется отдельный подход: создание контента, публикации, партнёрство или ручная заявка.</t>
+  </si>
+  <si>
     <t>Не является каталогом компаний</t>
   </si>
   <si>
     <t>Партнёрская платформа</t>
   </si>
   <si>
+    <t>Партнёрская программа (reseller/commission), публичного каталога агентств нет — только sales-lead формы (Demo/Pricing/Trial)</t>
+  </si>
+  <si>
     <t>Системный статус</t>
   </si>
   <si>
@@ -901,183 +902,219 @@
     <t>Примечания</t>
   </si>
   <si>
+    <t>BLOCKED</t>
+  </si>
+  <si>
+    <t>BLOCKED: Cloudflare 403 — 'Sorry, you have been blocked'; требуется ручной заход</t>
+  </si>
+  <si>
+    <t>Cloudflare</t>
+  </si>
+  <si>
+    <t>Блокировка сайта — не переоткрывать, перейти к следующим площадкам.</t>
+  </si>
+  <si>
+    <t>BLOCKED: Cloudflare 403 — 'Performing security verification'; требуется ручной заход</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FAILED: Cloudflare block (403) — 'Performing security verification'. Предыдущий SUCCESS не верифицирован. Домен недоступен для автоматизации.</t>
+  </si>
+  <si>
+    <t>NEEDS_MANUAL</t>
+  </si>
+  <si>
+    <t>REGISTERED (аккаунт создан: email itllect.marketing@gmail.com, CAPTCHA вручную). Онбординг остановлен на Business Identity Verification. SMS/Phone Call НЕ используем (не вводить личный телефон). Требуется Manual Verification через Support: Secretary of State registry URL, EIN, NMLS number (не придумывать EIN/NMLS). Публичный профиль НЕ создан. НЕ повторять регистрацию.</t>
+  </si>
+  <si>
+    <t>CF blocked in headless; needs headed stealth + manual solve</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>BLOCKED: Cloudflare 403 — 'Sorry, you have been blocked'; требуется ручной заход</t>
-  </si>
-  <si>
-    <t>Cloudflare</t>
-  </si>
-  <si>
-    <t>Блокировка сайта — не переоткрывать, перейти к следующим площадкам.</t>
-  </si>
-  <si>
-    <t>BLOCKED: Cloudflare 403 — 'Performing security verification'; требуется ручной заход</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>FAILED: Cloudflare block (403) — 'Performing security verification'. Предыдущий SUCCESS не верифицирован. Домен недоступен для автоматизации.</t>
-  </si>
-  <si>
-    <t>NEEDS_MANUAL</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE: 0f — перепроверить вручную</t>
+    <t>403/404</t>
+  </si>
+  <si>
+    <t>требуется регистрация/вход</t>
+  </si>
+  <si>
+    <t>FAILED: /registration=404, /login=404, /signup=403 (access denied). Площадка недоступна для автоматической регистрации.</t>
+  </si>
+  <si>
+    <t>claim-listing → 404 (Page not found), форма нерабочая</t>
+  </si>
+  <si>
+    <t>claim-listing = Page not found (404); форма нерабочая</t>
+  </si>
+  <si>
+    <t>SUBMITTED</t>
+  </si>
+  <si>
+    <t>SUBMITTED 07.08: заявка отправлена, профиль НЕ опубликован (поиск: Results Found 0) — ожидает email-подтверждения на info@itllect-agency.com / модерации</t>
+  </si>
+  <si>
+    <t>SUBMITTED 07.08: заявка отправлена (submit прошёл, SUCCESS-сигнал скрипта), но публичный профиль НЕ найден: поиск /search/business/itllect = Results Found 0 (проверено 4 вариациями). Вероятно, требуется email-подтверждение на info@itllect-agency.com (в ящике itllect.marketing@gmail.com писем от Brownbook нет). Статус VERIFIED_SUCCESS будет установлен после появления публичного профиля.</t>
+  </si>
+  <si>
+    <t>REPROBE 08.08: CF turnstile — multiple headed attempts failed, verification not passable; stay BLOCKED</t>
+  </si>
+  <si>
+    <t>Блокировка сайта — не переоткрывать, перейти к следующим площадкам.; REPROBE 2026-08-08: Site accessible, form detected — needs submission attempt; SUBMIT FAILED 08.08: CF turnstile not passable in headed mode either</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE</t>
+  </si>
+  <si>
+    <t>Площадка не подходит для размещения</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f</t>
+  </si>
+  <si>
+    <t>REPROBE 08.08: accessible but no add business form — not a business directory; status NOT_APPLICABLE</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; REPROBE 2026-08-08: n49 accessible but no business listing form — not a directory</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS: профиль создан и публично доступен (18+ млн бизнесов в каталоге)</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS: Профиль создан и публично доступен. URL: https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/. Аккаунт: itllect / DimaItllect2026!55. Заполнены: контакты, адрес, категория (Advertising - Direct Mail), описание. Email verification не требуется (аккаунт активирован сразу).</t>
+  </si>
+  <si>
+    <t>Подтверждено в headed-сессии 31.07 (turnstile решён, submit прошёл)</t>
+  </si>
+  <si>
+    <t>PREVIEW 3f OK; SUBMIT blocked by CF turnstile on /get-listed</t>
+  </si>
+  <si>
+    <t>Регистрация пройдена, профиль агентства заполнен вручную, отправлен</t>
+  </si>
+  <si>
+    <t>Login required; needs account creation before agency submission</t>
+  </si>
+  <si>
+    <t>CF blocked in headless; needs headed stealth + manual solve; REPROBE 2026-08-08: Site accessible, form detected — needs submission attempt; SUBMIT FAILED 08.08: CF not passable in headed mode</t>
+  </si>
+  <si>
+    <t>The Manifest has no own form (/listings/list-your-company = 404). /get-listed explains: registration via Clutch.co. CTA 'Create a Free Profile' -&gt; https://vendor.clutch.co/profile/create/basic (Basic tier, free). Main clutch.co/get-listed loads (CF clears ~30s; tiers: Basic Free / Verified $499/yr / Advertiser). But vendor.clutch.co CF challenge-loop: 'Verification successful. Waiting for vendor.clutch.co to respond' — origin does not respond (Ray ID a27c85757b9b543b). 2 attempts waited 120s and 288s, both stuck. 3 false-positive SUBMITTED outcomes reverted (0 fields). BLOCKED per site-handling rules — no loop reopening. Manual human session in regular browser may work.</t>
+  </si>
+  <si>
+    <t>сайт недоступен</t>
+  </si>
+  <si>
+    <t>Site unreachable (chrome-error)</t>
   </si>
   <si>
     <t>page.waitForTimeout: Target page, context or browser has been closed</t>
   </si>
   <si>
-    <t>CF blocked in headless; needs headed stealth + manual solve</t>
-  </si>
-  <si>
-    <t>403/404</t>
-  </si>
-  <si>
-    <t>требуется регистрация/вход</t>
-  </si>
-  <si>
-    <t>FAILED: /registration=404, /login=404, /signup=403 (access denied). Площадка недоступна для автоматической регистрации.</t>
-  </si>
-  <si>
-    <t>claim-listing → 404 (Page not found), форма нерабочая</t>
-  </si>
-  <si>
-    <t>claim-listing = Page not found (404); форма нерабочая</t>
-  </si>
-  <si>
-    <t>SUBMITTED</t>
-  </si>
-  <si>
-    <t>SUBMITTED 07.08: заявка отправлена, профиль НЕ опубликован (поиск: Results Found 0) — ожидает email-подтверждения на info@itllect-agency.com / модерации</t>
-  </si>
-  <si>
-    <t>SUBMITTED 07.08: заявка отправлена (submit прошёл, SUCCESS-сигнал скрипта), но публичный профиль НЕ найден: поиск /search/business/itllect = Results Found 0 (проверено 4 вариациями). Вероятно, требуется email-подтверждение на info@itllect-agency.com (в ящике itllect.marketing@gmail.com писем от Brownbook нет). Статус VERIFIED_SUCCESS будет установлен после появления публичного профиля.</t>
-  </si>
-  <si>
-    <t>EXTERNAL BLOCK — Cloudflare/access restriction; IP/fingerprint блокировка, turnstile не проходит ("Sorry, you have been blocked")</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE</t>
-  </si>
-  <si>
-    <t>Площадка не подходит для размещения</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE: 0f</t>
-  </si>
-  <si>
-    <t>VERIFIED_SUCCESS</t>
-  </si>
-  <si>
-    <t>VERIFIED_SUCCESS: профиль создан и публично доступен (18+ млн бизнесов в каталоге)</t>
-  </si>
-  <si>
-    <t>VERIFIED_SUCCESS: Профиль создан и публично доступен. URL: https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/. Аккаунт: itllect / DimaItllect2026!55. Заполнены: контакты, адрес, категория (Advertising - Direct Mail), описание. Email verification не требуется (аккаунт активирован сразу).</t>
-  </si>
-  <si>
-    <t>SUCCESS</t>
-  </si>
-  <si>
-    <t>Подтверждено в headed-сессии 31.07 (turnstile решён, submit прошёл)</t>
-  </si>
-  <si>
-    <t>PREVIEW 3f OK; SUBMIT blocked by CF turnstile on /get-listed</t>
-  </si>
-  <si>
-    <t>Регистрация пройдена, профиль агентства заполнен вручную, отправлен</t>
-  </si>
-  <si>
-    <t>Login required; needs account creation before agency submission</t>
+    <t>Login/registration required</t>
+  </si>
+  <si>
+    <t>SPA-форма 35f открывается; заполнение медленное, зависает — нужен ручной шаг</t>
+  </si>
+  <si>
+    <t>Ожил после DEAD; SPA; телефон в форме OPTIONAL (не обязателен); сервер нестабилен (500), переходы между шагами флаки 25-75s+; аккаунт НЕ создан; профиль human-bark-com зафлагован антиботом (SPA не рендерится) — работать через human-bark2</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS: профиль создан и публично доступен</t>
+  </si>
+  <si>
+    <t>VERIFIED_SUCCESS: Профиль создан и подтверждён. URL: https://www.semfirms.com/profile/itllect-llc. Аккаунт: itllect.marketing@gmail.com / DimaItllect2026!55. Блокировало: поле title требовало 'Itllect LLC' (полное юридическое название). Drupal валидация отклоняла форму без полного названия компании.</t>
+  </si>
+  <si>
+    <t>Форма жива на /registration (Drupal); заполнение проходит, submit зависает — нужен ручной шаг</t>
+  </si>
+  <si>
+    <t>OAuth-only: регистрация только через LinkedIn («Sign up with Linkedin»). Из автоматизации исключён — только ручной LinkedIn-вход. Подтверждено запуском: форма на /?#register не содержит email-поля, AI mapping 17 полей, Filled 2/18 (11 failed), ручное подтверждение за 180s не получено.</t>
+  </si>
+  <si>
+    <t>Регистрация пройдена, заявка add-agency отправлена</t>
+  </si>
+  <si>
+    <t>PREVIEW 4f OK; needs registration before add-agency</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 3f</t>
+  </si>
+  <si>
+    <t>Заявка на членство подана (человек подтвердил)</t>
+  </si>
+  <si>
+    <t>Paid membership platform, requires separate client approval and budget. Not included in standard directory submission workflow. GrowthZone multi-step form: tier selection (cheapest for-profit: New Member GENERAL-GFLCC $574/year + $50 one-time, non-refundable, auto-renewal with stored card) → contact info → payment.</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: create business page + postcard PIN verification. Local directory listing possible.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 2f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: create business page + postcard verify. Not NA.</t>
+  </si>
+  <si>
+    <t>SUBMITTED 07.08: заявка отправлена (reCAPTCHA v2 решена вручную), профиль НЕ опубликован (поиск: No result) — ожидает модерации</t>
+  </si>
+  <si>
+    <t>CAPTCHA (recaptcha_v2)</t>
+  </si>
+  <si>
+    <t>SUBMITTED 07.08: заявка отправлена (reCAPTCHA v2 решена вручную, submit прошёл), но публичный профиль НЕ найден: /biz/itllect=404, /biz/itllect-llc=404, /biz/itllect-agency=soft-404, поиск q=itllect = No result. Листинг, вероятно, на модерации (в ящике itllect.marketing@gmail.com писем нет; email формы: info@itllect-agency.com). VERIFIED_SUCCESS будет установлен после публикации профиля.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 1f</t>
+  </si>
+  <si>
+    <t>MASTER_LIST: NOT_APPLICABLE для listing (Government mentoring resource). Запуск подтвердил: реальной формы нет</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: list agency on agencies.semrush.com self-service flow.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: agencies.semrush.com has public directory with "List your agency" self-service flow.</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: partner application leads to public agency directory listing.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: ecosystem.hubspot.com has public agency directory. Partner app leads to listing.</t>
+  </si>
+  <si>
+    <t>REGISTERED</t>
+  </si>
+  <si>
+    <t>Partner-аккаунт создан</t>
+  </si>
+  <si>
+    <t>Page loaded but no form detected</t>
+  </si>
+  <si>
+    <t>Form fields not found by Playwright</t>
+  </si>
+  <si>
+    <t>Partner ecosystem (reseller/commission program), не бизнес-каталог — /partner содержит только sales-lead формы (Demo/Pricing/Trial), публичного каталога агентств нет</t>
+  </si>
+  <si>
+    <t>Partner ecosystem, not a business directory. ActiveCampaign is a SaaS marketing-automation platform with an Agency Partner / Certified Consultant / White-Label program. The /partner page only has sales-lead capture forms (Request a Demo, Request Pricing, Free trial) — submitting them generates sales leads for ActiveCampaign, NOT a public company profile or directory listing. No public directory of agencies exists. Partner application requires talking to sales (/partner/contact) and/or logging into a separate reseller portal (partner-auth.activecampaign.com). Note: queue URL /partners/become-a-partner returns 404; live page is /partner. Not a citation/listing channel — NOT_APPLICABLE. No account or test registration created.</t>
   </si>
   <si>
     <t>Окно ручного действия истекло (180с) — требуется повтор</t>
   </si>
   <si>
-    <t>Page loaded but no form detected</t>
-  </si>
-  <si>
-    <t>сайт недоступен</t>
-  </si>
-  <si>
-    <t>Site unreachable (chrome-error)</t>
-  </si>
-  <si>
-    <t>Login/registration required</t>
-  </si>
-  <si>
-    <t>SPA-форма 35f открывается; заполнение медленное, зависает — нужен ручной шаг</t>
-  </si>
-  <si>
-    <t>Ожил после DEAD; SPA 35f; заполняется медленно, зависает</t>
-  </si>
-  <si>
-    <t>VERIFIED_SUCCESS: профиль создан и публично доступен</t>
-  </si>
-  <si>
-    <t>VERIFIED_SUCCESS: Профиль создан и подтверждён. URL: https://www.semfirms.com/profile/itllect-llc. Аккаунт: itllect.marketing@gmail.com / DimaItllect2026!55. Блокировало: поле title требовало 'Itllect LLC' (полное юридическое название). Drupal валидация отклоняла форму без полного названия компании.</t>
-  </si>
-  <si>
-    <t>Форма жива на /registration (Drupal); заполнение проходит, submit зависает — нужен ручной шаг</t>
-  </si>
-  <si>
-    <t>OAuth-only: регистрация только через LinkedIn («Sign up with Linkedin»). Из автоматизации исключён — только ручной LinkedIn-вход.</t>
-  </si>
-  <si>
-    <t>Регистрация пройдена, заявка add-agency отправлена</t>
-  </si>
-  <si>
-    <t>PREVIEW 4f OK; needs registration before add-agency</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE: 3f</t>
-  </si>
-  <si>
-    <t>Заявка на членство подана (человек подтвердил)</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE: 2f</t>
-  </si>
-  <si>
-    <t>SUBMITTED 07.08: заявка отправлена (reCAPTCHA v2 решена вручную), профиль НЕ опубликован (поиск: No result) — ожидает модерации</t>
-  </si>
-  <si>
-    <t>CAPTCHA (recaptcha_v2)</t>
-  </si>
-  <si>
-    <t>SUBMITTED 07.08: заявка отправлена (reCAPTCHA v2 решена вручную, submit прошёл), но публичный профиль НЕ найден: /biz/itllect=404, /biz/itllect-llc=404, /biz/itllect-agency=soft-404, поиск q=itllect = No result. Листинг, вероятно, на модерации (в ящике itllect.marketing@gmail.com писем нет; email формы: info@itllect-agency.com). VERIFIED_SUCCESS будет установлен после публикации профиля.</t>
-  </si>
-  <si>
-    <t>NOT_APPLICABLE: 1f</t>
-  </si>
-  <si>
-    <t>PENDING</t>
-  </si>
-  <si>
-    <t>FORM_READY: 29f</t>
-  </si>
-  <si>
-    <t>REGISTERED</t>
-  </si>
-  <si>
-    <t>Partner-аккаунт создан</t>
-  </si>
-  <si>
-    <t>Form fields not found by Playwright</t>
-  </si>
-  <si>
-    <t>Сайт ожил после DEAD; partner-форма 21f заполнена частично, submit-кнопки нет</t>
-  </si>
-  <si>
-    <t>Ожил после DEAD; partner form 21f, заполнено частично (email)</t>
-  </si>
-  <si>
     <t>Аккаунт создан в headed-сессии; CF обойдён вручную</t>
   </si>
   <si>
+    <t>RECLASSIFIED 08.08: create startup/company profile. Startup directory listing possible.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: startup directory. Company CAN create profile.</t>
+  </si>
+  <si>
     <t>Brand channel создан (человек подтвердил)</t>
   </si>
   <si>
@@ -1093,22 +1130,31 @@
     <t>Aweber email capture (form-sorry?message=notactivecustomer), не листинг</t>
   </si>
   <si>
-    <t>Аккаунт создавался ранее; повторный прогон не стартовал (ошибка браузера)</t>
-  </si>
-  <si>
-    <t>CAPTCHA (turnstile)</t>
-  </si>
-  <si>
-    <t>Captcha detected</t>
-  </si>
-  <si>
-    <t>Connection blocked</t>
-  </si>
-  <si>
-    <t>FAILED: ERR_CONNECTION_CLOSED — сайт блокирует соединение (возможно Cloudflare/антибот или гео-блокировка).</t>
+    <t>RECLASSIFIED 08.08: claim business + domain verification required. Listing IS possible.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per NOT_APPLICABLE audit 08.08: claim business + domain verify. Not NA — listing IS possible.</t>
+  </si>
+  <si>
+    <t>REPROBE 08.08: site accessible (en-us/), form 10 fields detected, EMAIL fields absent — HUMAN ACTION timeout; stay NEEDS_MANUAL</t>
+  </si>
+  <si>
+    <t>FAILED: ERR_CONNECTION_CLOSED — сайт блокирует соединение (возможно Cloudflare/антибот или гео-блокировка).; REPROBE 2026-08-08: Site accessible, form detected — needs submission attempt</t>
   </si>
   <si>
     <t>Сайт ожил после DEAD; claim-listing закрыт Cloudflare; повторный прогон упал (краш браузера)</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: claim InfoGroup citation listing via phone/postcard.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: claim InfoGroup listing via phone/postcard. Not NA.</t>
+  </si>
+  <si>
+    <t>RECLASSIFIED 08.08: claim venue + phone verification required. Business CAN be listed.</t>
+  </si>
+  <si>
+    <t>NOT_APPLICABLE: 0f; RECLASSIFIED 08.08: NOT_APPLICABLE → NEEDS_MANUAL per audit 08.08: claim venue + phone verify. Business CAN be listed.</t>
   </si>
 </sst>
 </file>
@@ -1518,7 +1564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1617,7 +1663,7 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
@@ -1628,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -1639,48 +1685,64 @@
         <v>22</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="16" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-    </row>
-    <row r="21" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>31</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
     </row>
@@ -1689,22 +1751,39 @@
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
     </row>
-    <row r="26" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
+    <row r="27" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" ht="16" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A18:C21"/>
-    <mergeCell ref="A24:C27"/>
+    <mergeCell ref="A22:C25"/>
+    <mergeCell ref="A28:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1713,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1730,2466 +1809,2434 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
         <v>48</v>
       </c>
-      <c r="B4" t="s">
+      <c r="H4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>44</v>
-      </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
         <v>56</v>
       </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
         <v>50</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" t="s">
-        <v>44</v>
-      </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
         <v>50</v>
       </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="s">
-        <v>44</v>
-      </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" t="s">
         <v>100</v>
       </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" t="s">
         <v>50</v>
       </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" t="s">
-        <v>44</v>
-      </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
         <v>101</v>
       </c>
-      <c r="B18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>94</v>
-      </c>
       <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" t="s">
         <v>50</v>
       </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" t="s">
-        <v>55</v>
-      </c>
       <c r="J18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J20" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" t="s">
         <v>50</v>
       </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" t="s">
-        <v>53</v>
-      </c>
-      <c r="I21" t="s">
-        <v>55</v>
-      </c>
       <c r="J21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H22" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J22" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J23" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H24" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J25" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H26" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I26" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H27" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H28" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I28" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H29" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J29" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H30" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H31" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="I31" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="J31" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H32" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I32" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
         <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="H33" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J33" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I34" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J34" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B35" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H35" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I35" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J35" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="H36" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I36" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J36" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H37" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I37" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J37" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H38" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I38" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J38" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H39" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="I39" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="J39" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D40" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E40" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G40" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H40" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I40" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>175</v>
+      </c>
+      <c r="B41" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" t="s">
         <v>169</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
         <v>170</v>
       </c>
-      <c r="C41" t="s">
-        <v>163</v>
-      </c>
-      <c r="D41" t="s">
-        <v>164</v>
-      </c>
       <c r="E41" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H41" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I41" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J41" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C42" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D42" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F42" t="s">
         <v>22</v>
       </c>
       <c r="G42" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="H42" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J42" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D43" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F43" t="s">
         <v>22</v>
       </c>
       <c r="G43" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="H43" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J43" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C44" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E44" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H44" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I44" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J44" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B45" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D45" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I45" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J45" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D46" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E46" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G46" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="H46" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I46" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J46" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D47" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G47" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H47" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J47" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E48" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G48" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H48" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="I48" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="J48" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B49" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D49" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E49" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G49" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H49" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J49" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B50" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C50" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D50" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E50" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I50" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J50" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B51" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C51" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D51" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E51" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H51" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I51" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J51" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B52" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C52" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D52" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G52" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H52" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J52" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" t="s">
+        <v>205</v>
+      </c>
+      <c r="D53" t="s">
         <v>206</v>
       </c>
-      <c r="B53" t="s">
-        <v>207</v>
-      </c>
-      <c r="C53" t="s">
-        <v>199</v>
-      </c>
-      <c r="D53" t="s">
-        <v>200</v>
-      </c>
       <c r="E53" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H53" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I53" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J53" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C54" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D54" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F54" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H54" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I54" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J54" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B55" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C55" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D55" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E55" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H55" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I55" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J55" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D56" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F56" t="s">
         <v>22</v>
       </c>
       <c r="G56" t="s">
-        <v>217</v>
+        <v>59</v>
       </c>
       <c r="H56" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J56" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B57" t="s">
+        <v>224</v>
+      </c>
+      <c r="C57" t="s">
         <v>219</v>
       </c>
-      <c r="C57" t="s">
-        <v>213</v>
-      </c>
       <c r="D57" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E57" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F57" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H57" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I57" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J57" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B58" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D58" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E58" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="G58" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="H58" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I58" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J58" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B59" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C59" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D59" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E59" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F59" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H59" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I59" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J59" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C60" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D60" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E60" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H60" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I60" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J60" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" t="s">
+        <v>236</v>
+      </c>
+      <c r="C61" t="s">
         <v>230</v>
       </c>
-      <c r="B61" t="s">
-        <v>231</v>
-      </c>
-      <c r="C61" t="s">
-        <v>225</v>
-      </c>
       <c r="D61" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F61" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H61" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I61" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J61" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B62" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D62" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E62" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F62" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G62" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H62" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I62" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J62" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C63" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D63" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E63" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H63" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I63" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J63" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D64" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F64" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G64" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H64" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I64" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J64" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B65" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C65" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D65" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F65" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G65" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H65" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I65" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B66" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D66" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F66" t="s">
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H66" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I66" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J66" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D67" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E67" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="H67" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I67" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J67" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>257</v>
+      </c>
+      <c r="B68" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68" t="s">
         <v>252</v>
       </c>
-      <c r="B68" t="s">
-        <v>253</v>
-      </c>
-      <c r="C68" t="s">
-        <v>247</v>
-      </c>
       <c r="D68" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E68" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H68" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I68" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J68" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B69" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C69" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D69" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E69" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F69" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G69" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H69" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I69" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J69" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E70" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F70" t="s">
         <v>22</v>
       </c>
       <c r="G70" t="s">
-        <v>261</v>
+        <v>59</v>
       </c>
       <c r="H70" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J70" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E71" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G71" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H71" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J71" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" t="s">
+        <v>270</v>
+      </c>
+      <c r="C72" t="s">
+        <v>264</v>
+      </c>
+      <c r="D72" t="s">
         <v>265</v>
       </c>
-      <c r="B72" t="s">
-        <v>266</v>
-      </c>
-      <c r="C72" t="s">
-        <v>259</v>
-      </c>
-      <c r="D72" t="s">
-        <v>260</v>
-      </c>
       <c r="E72" t="s">
+        <v>56</v>
+      </c>
+      <c r="F72" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" t="s">
+        <v>48</v>
+      </c>
+      <c r="H72" t="s">
+        <v>49</v>
+      </c>
+      <c r="I72" t="s">
         <v>50</v>
       </c>
-      <c r="F72" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" t="s">
-        <v>267</v>
-      </c>
-      <c r="H72" t="s">
-        <v>43</v>
-      </c>
-      <c r="I72" t="s">
-        <v>44</v>
-      </c>
       <c r="J72" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B73" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="D73" t="s">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="E73" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G73" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H73" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="I73" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B74" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C74" t="s">
         <v>273</v>
       </c>
       <c r="D74" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E74" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="F74" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G74" t="s">
         <v>274</v>
       </c>
       <c r="H74" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I74" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J74" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B75" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C75" t="s">
         <v>273</v>
       </c>
       <c r="D75" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E75" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F75" t="s">
         <v>22</v>
       </c>
       <c r="G75" t="s">
-        <v>274</v>
+        <v>59</v>
       </c>
       <c r="H75" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I75" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J75" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B76" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C76" t="s">
         <v>273</v>
       </c>
       <c r="D76" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E76" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F76" t="s">
         <v>22</v>
       </c>
       <c r="G76" t="s">
-        <v>279</v>
+        <v>59</v>
       </c>
       <c r="H76" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I76" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J76" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>280</v>
-      </c>
-      <c r="B77" t="s">
-        <v>281</v>
-      </c>
-      <c r="C77" t="s">
-        <v>273</v>
-      </c>
-      <c r="D77" t="s">
-        <v>164</v>
-      </c>
-      <c r="E77" t="s">
-        <v>50</v>
-      </c>
-      <c r="F77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G77" t="s">
-        <v>282</v>
-      </c>
-      <c r="H77" t="s">
-        <v>80</v>
-      </c>
-      <c r="I77" t="s">
-        <v>81</v>
-      </c>
-      <c r="J77" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -4200,7 +4247,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -4212,393 +4259,631 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s">
-        <v>195</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="B20" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>214</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="B22" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C24" t="s">
         <v>16</v>
       </c>
-      <c r="D23" t="s">
-        <v>248</v>
-      </c>
-      <c r="E23" t="s">
-        <v>181</v>
+      <c r="D24" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B26" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>232</v>
+      </c>
+      <c r="B31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>234</v>
+      </c>
+      <c r="E31" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>250</v>
+      </c>
+      <c r="B32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
+        <v>253</v>
+      </c>
+      <c r="E32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>262</v>
+      </c>
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+      <c r="C33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>266</v>
+      </c>
+      <c r="B34" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
+        <v>268</v>
+      </c>
+      <c r="E34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>269</v>
+      </c>
+      <c r="B35" t="s">
+        <v>270</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>277</v>
+      </c>
+      <c r="B36" t="s">
+        <v>278</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B37" t="s">
+        <v>280</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4609,7 +4894,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -4620,422 +4905,366 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" t="s">
         <v>285</v>
-      </c>
-      <c r="D12" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D16" t="s">
         <v>288</v>
-      </c>
-      <c r="D16" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D17" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C18" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D18" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C19" t="s">
         <v>286</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D20" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D22" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D26" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>271</v>
-      </c>
-      <c r="B27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C27" t="s">
-        <v>285</v>
-      </c>
-      <c r="D27" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>275</v>
-      </c>
-      <c r="B28" t="s">
-        <v>276</v>
-      </c>
-      <c r="C28" t="s">
-        <v>285</v>
-      </c>
-      <c r="D28" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>277</v>
-      </c>
-      <c r="B29" t="s">
-        <v>278</v>
-      </c>
-      <c r="C29" t="s">
-        <v>288</v>
-      </c>
-      <c r="D29" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>280</v>
-      </c>
-      <c r="B30" t="s">
-        <v>281</v>
-      </c>
-      <c r="C30" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" t="s">
-        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -5046,7 +5275,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -5060,10 +5289,10 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>289</v>
@@ -5075,7 +5304,7 @@
         <v>291</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>292</v>
@@ -5083,10 +5312,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
         <v>293</v>
@@ -5106,10 +5335,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
         <v>293</v>
@@ -5129,10 +5358,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
         <v>293</v>
@@ -5152,10 +5381,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
         <v>300</v>
@@ -5175,10 +5404,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
         <v>293</v>
@@ -5193,21 +5422,21 @@
         <v>295</v>
       </c>
       <c r="G6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D7" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E7" t="s">
         <v>304</v>
@@ -5221,16 +5450,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D8" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E8" t="s">
         <v>307</v>
@@ -5244,10 +5473,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>293</v>
@@ -5262,15 +5491,15 @@
         <v>295</v>
       </c>
       <c r="G9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>309</v>
@@ -5290,10 +5519,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
         <v>293</v>
@@ -5308,130 +5537,130 @@
         <v>298</v>
       </c>
       <c r="G11" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F12" t="s">
         <v>298</v>
       </c>
       <c r="G12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E13" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F13" t="s">
         <v>298</v>
       </c>
       <c r="G13" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F14" t="s">
         <v>298</v>
       </c>
       <c r="G14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
         <v>309</v>
       </c>
       <c r="D15" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F15" t="s">
         <v>298</v>
       </c>
       <c r="G15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
         <v>309</v>
       </c>
       <c r="D16" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F16" t="s">
         <v>298</v>
       </c>
       <c r="G16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
         <v>293</v>
@@ -5440,113 +5669,113 @@
         <v>293</v>
       </c>
       <c r="E17" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="F17" t="s">
         <v>295</v>
       </c>
       <c r="G17" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D18" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E18" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F18" t="s">
         <v>298</v>
       </c>
       <c r="G18" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D19" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D20" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E20" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F20" t="s">
         <v>305</v>
       </c>
       <c r="G20" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D21" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E21" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="F21" t="s">
         <v>295</v>
       </c>
       <c r="G21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
         <v>300</v>
@@ -5555,274 +5784,274 @@
         <v>300</v>
       </c>
       <c r="E22" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F22" t="s">
         <v>298</v>
       </c>
       <c r="G22" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D23" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E23" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F23" t="s">
         <v>305</v>
       </c>
       <c r="G23" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E24" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F24" t="s">
         <v>298</v>
       </c>
       <c r="G24" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E25" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F25" t="s">
         <v>298</v>
       </c>
       <c r="G25" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F26" t="s">
         <v>298</v>
       </c>
       <c r="G26" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
         <v>309</v>
       </c>
       <c r="D27" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F27" t="s">
         <v>298</v>
       </c>
       <c r="G27" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D28" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E28" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F28" t="s">
         <v>298</v>
       </c>
       <c r="G28" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
         <v>309</v>
       </c>
       <c r="D29" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E29" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F29" t="s">
         <v>305</v>
       </c>
       <c r="G29" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F30" t="s">
         <v>298</v>
       </c>
       <c r="G30" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D31" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="E31" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="F31" t="s">
         <v>305</v>
       </c>
       <c r="G31" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F32" t="s">
         <v>298</v>
       </c>
       <c r="G32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D33" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E33" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="F33" t="s">
         <v>298</v>
       </c>
       <c r="G33" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
         <v>309</v>
@@ -5831,297 +6060,297 @@
         <v>309</v>
       </c>
       <c r="E34" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="G34" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B35" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D35" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F35" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G35" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C36" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F36" t="s">
         <v>295</v>
       </c>
       <c r="G36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D37" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F37" t="s">
         <v>298</v>
       </c>
       <c r="G37" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D38" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F38" t="s">
         <v>298</v>
       </c>
       <c r="G38" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="D39" t="s">
-        <v>344</v>
+        <v>314</v>
       </c>
       <c r="E39" t="s">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="F39" t="s">
         <v>298</v>
       </c>
       <c r="G39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E40" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F40" t="s">
         <v>298</v>
       </c>
       <c r="G40" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B41" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C41" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D41" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E41" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F41" t="s">
         <v>298</v>
       </c>
       <c r="G41" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C42" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D42" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E42" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="F42" t="s">
         <v>298</v>
       </c>
       <c r="G42" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D43" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E43" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="F43" t="s">
         <v>298</v>
       </c>
       <c r="G43" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C44" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D44" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="E44" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="F44" t="s">
         <v>298</v>
       </c>
       <c r="G44" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B45" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C45" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D45" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E45" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F45" t="s">
         <v>298</v>
       </c>
       <c r="G45" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E46" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F46" t="s">
         <v>298</v>
       </c>
       <c r="G46" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C47" t="s">
         <v>300</v>
@@ -6130,44 +6359,44 @@
         <v>300</v>
       </c>
       <c r="E47" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F47" t="s">
         <v>305</v>
       </c>
       <c r="G47" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B48" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C48" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D48" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="E48" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F48" t="s">
         <v>298</v>
       </c>
       <c r="G48" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B49" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C49" t="s">
         <v>300</v>
@@ -6176,67 +6405,67 @@
         <v>300</v>
       </c>
       <c r="E49" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="F49" t="s">
         <v>298</v>
       </c>
       <c r="G49" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B50" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C50" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D50" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F50" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B51" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C51" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D51" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E51" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F51" t="s">
         <v>305</v>
       </c>
       <c r="G51" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B52" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C52" t="s">
         <v>300</v>
@@ -6245,458 +6474,458 @@
         <v>300</v>
       </c>
       <c r="E52" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F52" t="s">
         <v>305</v>
       </c>
       <c r="G52" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B53" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C53" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D53" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F53" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G53" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F54" t="s">
         <v>298</v>
       </c>
       <c r="G54" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B55" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C55" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="E55" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F55" t="s">
         <v>295</v>
       </c>
       <c r="G55" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C56" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D56" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E56" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="F56" t="s">
         <v>298</v>
       </c>
       <c r="G56" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C57" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E57" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F57" t="s">
         <v>298</v>
       </c>
       <c r="G57" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B58" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C58" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D58" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E58" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F58" t="s">
         <v>295</v>
       </c>
       <c r="G58" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B59" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E59" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F59" t="s">
         <v>298</v>
       </c>
       <c r="G59" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C60" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="E60" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="F60" t="s">
         <v>305</v>
       </c>
       <c r="G60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C61" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D61" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E61" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F61" t="s">
         <v>298</v>
       </c>
       <c r="G61" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B62" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D62" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E62" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F62" t="s">
         <v>298</v>
       </c>
       <c r="G62" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C63" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D63" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E63" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="F63" t="s">
         <v>305</v>
       </c>
       <c r="G63" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D64" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E64" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F64" t="s">
         <v>298</v>
       </c>
       <c r="G64" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B65" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C65" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D65" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E65" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F65" t="s">
         <v>298</v>
       </c>
       <c r="G65" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B66" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D66" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="E66" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="F66" t="s">
         <v>305</v>
       </c>
       <c r="G66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B67" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C67" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D67" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E67" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="F67" t="s">
         <v>305</v>
       </c>
       <c r="G67" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B68" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C68" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D68" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E68" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F68" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G68" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B69" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E69" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F69" t="s">
         <v>298</v>
       </c>
       <c r="G69" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C70" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D70" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E70" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="F70" t="s">
         <v>298</v>
       </c>
       <c r="G70" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C71" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D71" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E71" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="F71" t="s">
-        <v>358</v>
+        <v>305</v>
       </c>
       <c r="G71" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C72" t="s">
         <v>293</v>
@@ -6705,128 +6934,105 @@
         <v>293</v>
       </c>
       <c r="E72" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="F72" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G72" t="s">
-        <v>361</v>
+        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B73" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C73" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="D73" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="E73" t="s">
-        <v>362</v>
+        <v>315</v>
       </c>
       <c r="F73" t="s">
         <v>298</v>
       </c>
       <c r="G73" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B74" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C74" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D74" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E74" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F74" t="s">
         <v>298</v>
       </c>
       <c r="G74" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B75" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C75" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D75" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E75" t="s">
-        <v>314</v>
+        <v>374</v>
       </c>
       <c r="F75" t="s">
         <v>298</v>
       </c>
       <c r="G75" t="s">
-        <v>315</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B76" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C76" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D76" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E76" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="F76" t="s">
         <v>298</v>
       </c>
       <c r="G76" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>280</v>
-      </c>
-      <c r="B77" t="s">
-        <v>281</v>
-      </c>
-      <c r="C77" t="s">
-        <v>313</v>
-      </c>
-      <c r="D77" t="s">
-        <v>313</v>
-      </c>
-      <c r="E77" t="s">
-        <v>314</v>
-      </c>
-      <c r="F77" t="s">
-        <v>298</v>
-      </c>
-      <c r="G77" t="s">
-        <v>315</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/client-report/client-directory-report.xlsx
+++ b/client-report/client-directory-report.xlsx
@@ -986,7 +986,7 @@
     <t>VERIFIED_SUCCESS: профиль создан и публично доступен (18+ млн бизнесов в каталоге)</t>
   </si>
   <si>
-    <t>VERIFIED_SUCCESS: Профиль создан и публично доступен. URL: https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/. Аккаунт: itllect / DimaItllect2026!55. Заполнены: контакты, адрес, категория (Advertising - Direct Mail), описание. Email verification не требуется (аккаунт активирован сразу).</t>
+    <t>VERIFIED_SUCCESS: Профиль создан и публично доступен. URL: https://www.find-us-here.com/businesses/Itllect-LLC-Plantation-Florida-USA/34578398/. Аккаунт: itllect / [REDACTED]. Заполнены: контакты, адрес, категория (Advertising - Direct Mail), описание. Email verification не требуется (аккаунт активирован сразу).</t>
   </si>
   <si>
     <t>Подтверждено в headed-сессии 31.07 (turnstile решён, submit прошёл)</t>
@@ -1028,7 +1028,7 @@
     <t>VERIFIED_SUCCESS: профиль создан и публично доступен</t>
   </si>
   <si>
-    <t>VERIFIED_SUCCESS: Профиль создан и подтверждён. URL: https://www.semfirms.com/profile/itllect-llc. Аккаунт: itllect.marketing@gmail.com / DimaItllect2026!55. Блокировало: поле title требовало 'Itllect LLC' (полное юридическое название). Drupal валидация отклоняла форму без полного названия компании.</t>
+    <t>VERIFIED_SUCCESS: Профиль создан и подтверждён. URL: https://www.semfirms.com/profile/itllect-llc. Аккаунт: itllect.marketing@gmail.com / [REDACTED]. Блокировало: поле title требовало 'Itllect LLC' (полное юридическое название). Drupal валидация отклоняла форму без полного названия компании.</t>
   </si>
   <si>
     <t>Форма жива на /registration (Drupal); заполнение проходит, submit зависает — нужен ручной шаг</t>
@@ -1786,7 +1786,7 @@
     <mergeCell ref="A28:C31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4241,7 +4241,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4888,7 +4888,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5269,7 +5269,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -7037,6 +7037,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>